--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["hero-banner","hero-banner","hero-banner","hero-banner","hero-banner","hero-banner","carousel-product","carousel-product","columns-diptych","columns-diptych","columns-diptych","columns-diptych","cards-category","embed-social","cards-feature","cards-service"]</t>
+    <t>["hero-banner","hero-banner","hero-banner","carousel-product","carousel-product","columns-diptych","columns-diptych","cards-category","embed-social","cards-feature","cards-service"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-03-25T16:16:18.483Z</t>
+    <t>2026-03-25T19:19:02.259Z</t>
   </si>
   <si>
     <t>Faherty Brand - Official Site - Free Shipping on Orders $150+</t>
